--- a/docs/01需求矩阵第4组张芮萌.xlsx
+++ b/docs/01需求矩阵第4组张芮萌.xlsx
@@ -1,113 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
-  </bookViews>
-  <sheets>
-    <sheet name="需求进度管理表" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="示例" sheetId="2" state="visible" r:id="rId3"/>
-  </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
-  <definedNames>
-    <definedName function="false" hidden="false" name="Activity" vbProcedure="false">"'[1]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="bigmodel" vbProcedure="false">OFFSET([1]基本信息!$A$1,0,0,COUNTA([1]基本信息!$A$1)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="CMRight" vbProcedure="false">"'[3]'!$l$6":"$l$10"</definedName>
-    <definedName function="false" hidden="false" name="crlist" vbProcedure="false">OFFSET([1]Review记录!$A$3,0,0,COUNTA([1]Review记录!$K$1:$K$1048576),24)</definedName>
-    <definedName function="false" hidden="false" name="endcol" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="endline" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="from" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="KOUMOKUSUU" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="moduleList" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="Module_num" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="question" vbProcedure="false">OFFSET([1]Review记录!$K$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="questionType" vbProcedure="false">OFFSET([1]Review记录!$Q$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="reporter" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-3,1)</definedName>
-    <definedName function="false" hidden="false" name="ReviewKind" vbProcedure="false">[2]信息定义!$H$6:$H$8</definedName>
-    <definedName function="false" hidden="false" name="StatOKNG" vbProcedure="false">[2]信息定义!$J$6:$J$11</definedName>
-    <definedName function="false" hidden="false" name="StatOpenClose" vbProcedure="false">[2]信息定义!$K$6:$K$10</definedName>
-    <definedName function="false" hidden="false" name="status" vbProcedure="false">OFFSET([1]Review记录!$V$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="StatYesNo" vbProcedure="false">[2]信息定义!$I$6:$I$10</definedName>
-    <definedName function="false" hidden="false" name="TestPhase" vbProcedure="false">"'[1]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="total" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$Z$1:$Z$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="worker" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</definedName>
-    <definedName function="false" hidden="false" name="一级标题" vbProcedure="false">"'[5]'!$b$1"</definedName>
-    <definedName function="false" hidden="false" name="产品名称与版本" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="产品效益分析" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="产品概述" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="产品目标" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="产品目标市场" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="产品竞争分析" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="任务分解" vbProcedure="false">"'[3]'!$b$54"</definedName>
-    <definedName function="false" hidden="false" name="供方协定管理计划" vbProcedure="false">"'[3]'!$b$165"</definedName>
-    <definedName function="false" hidden="false" name="信息内容" vbProcedure="false">"'[3]'!$b$2"</definedName>
-    <definedName function="false" hidden="false" name="假定约束条件" vbProcedure="false">"'[3]'!$b$14"</definedName>
-    <definedName function="false" hidden="false" name="共利益者管理" vbProcedure="false">"'[3]'!$b$168"</definedName>
-    <definedName function="false" hidden="false" name="关键依赖关系" vbProcedure="false">"'[3]'!$b$174"</definedName>
-    <definedName function="false" hidden="false" name="关键问题" vbProcedure="false">"'[3]'!$b$25"</definedName>
-    <definedName function="false" hidden="false" name="决策分析计划" vbProcedure="false">"'[3]'!$b$182"</definedName>
-    <definedName function="false" hidden="false" name="可升级目标" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="可用性目标" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="可维护性目标" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="可靠性目标" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="培训计划" vbProcedure="false">"'[3]'!$b$149"</definedName>
-    <definedName function="false" hidden="false" name="子活动类型名" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="客户财产" vbProcedure="false">"'[3]'!$b$130"</definedName>
-    <definedName function="false" hidden="false" name="度量计划" vbProcedure="false">"'[3]'!$b$186"</definedName>
-    <definedName function="false" hidden="false" name="成本预算" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="模块" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="沟通" vbProcedure="false">"'[3]'!$b$169"</definedName>
-    <definedName function="false" hidden="false" name="父活动类型名" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="生命周期模型选定" vbProcedure="false">"'[3]'!$b$46"</definedName>
-    <definedName function="false" hidden="false" name="约束条件" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="规模与工作量估计" vbProcedure="false">"'[3]'!$b$56"</definedName>
-    <definedName function="false" hidden="false" name="规模和工作量估计" vbProcedure="false">"'[3]'!$b$73"</definedName>
-    <definedName function="false" hidden="false" name="识别知识和技能" vbProcedure="false">"'[3]'!$b$138"</definedName>
-    <definedName function="false" hidden="false" name="识别项目风险" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="质量保证计划" vbProcedure="false">"'[3]'!$b$206"</definedName>
-    <definedName function="false" hidden="false" name="软件复用" vbProcedure="false">"'[3]'!$b$88"</definedName>
-    <definedName function="false" hidden="false" name="运行环境" vbProcedure="false">"'[3]'!$b$116"</definedName>
-    <definedName function="false" hidden="false" name="配置管理" vbProcedure="false">"'[3]'!$b$209"</definedName>
-    <definedName function="false" hidden="false" name="配置管理计划" vbProcedure="false">"'[3]'!$b$201"</definedName>
-    <definedName function="false" hidden="false" name="里程碑" vbProcedure="false">NA()</definedName>
-    <definedName function="false" hidden="false" name="需求信息" vbProcedure="false">"'[3]'!$b$29"</definedName>
-    <definedName function="false" hidden="false" name="需求开发工具" vbProcedure="false">"'[3]'!$b$35"</definedName>
-    <definedName function="false" hidden="false" name="项目专属资源" vbProcedure="false">"'[3]'!$b$95"</definedName>
-    <definedName function="false" hidden="false" name="项目估计" vbProcedure="false">"'[3]'!$b$72"</definedName>
-    <definedName function="false" hidden="false" name="项目信息" vbProcedure="false">"'[3]'!$b$1"</definedName>
-    <definedName function="false" hidden="false" name="项目名称" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="项目培训" vbProcedure="false">"'[3]'!$b$137"</definedName>
-    <definedName function="false" hidden="false" name="项目基本信息" vbProcedure="false">"'[3]'!$b$5"</definedName>
-    <definedName function="false" hidden="false" name="项目概述" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="项目监控计划" vbProcedure="false">"'[3]'!$b$157"</definedName>
-    <definedName function="false" hidden="false" name="项目目标" vbProcedure="false">"'[3]'!$b$22"</definedName>
-    <definedName function="false" hidden="false" name="项目目的" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="项目组角色与职责" vbProcedure="false">"'[3]'!$b$97"</definedName>
-    <definedName function="false" hidden="false" name="项目范围" vbProcedure="false">"'[3]'!$b$53"</definedName>
-    <definedName function="false" hidden="false" name="项目规模" vbProcedure="false">"'[3]'!$a$1"</definedName>
-    <definedName function="false" hidden="false" name="项目资源" vbProcedure="false">"'[3]'!$b$96"</definedName>
-    <definedName function="false" hidden="false" name="项目过程定义" vbProcedure="false">"'[3]'!$b$45"</definedName>
-    <definedName function="false" hidden="false" name="项目过程裁剪" vbProcedure="false">"'[3]'!$b$50"</definedName>
-    <definedName function="false" hidden="false" name="项目阶段和里程碑" vbProcedure="false">"'[3]'!$b$58"</definedName>
-    <definedName function="false" hidden="false" name="项目需求" vbProcedure="false">"'[3]'!$b$28"</definedName>
-    <definedName function="false" hidden="false" name="风险管理" vbProcedure="false">"'[3]'!$b$202"</definedName>
-    <definedName function="false" hidden="false" name="风险管理计划" vbProcedure="false">"'[3]'!$b$194"</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="Print_Titles" vbProcedure="false">需求进度管理表!$1:$3</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="Print_Titles" vbProcedure="false">示例!$1:$3</definedName>
-  </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
-  </extLst>
-</workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ns2="http://schemas.libreoffice.org/">
+  <ns0:fileVersion appName="Calc"/>
+  <ns0:workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <ns0:workbookProtection/>
+  <ns0:bookViews>
+    <ns0:workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+  </ns0:bookViews>
+  <ns0:sheets>
+    <ns0:sheet name="需求进度管理表" sheetId="1" state="visible" ns1:id="rId2"/>
+    <ns0:sheet name="历史模板_非本项目" sheetId="2" state="visible" ns1:id="rId3"/>
+  </ns0:sheets>
+  <ns0:externalReferences>
+    <ns0:externalReference ns1:id="rId4"/>
+    <ns0:externalReference ns1:id="rId5"/>
+  </ns0:externalReferences>
+  <ns0:definedNames>
+    <ns0:definedName function="false" hidden="false" name="Activity" vbProcedure="false">"'[1]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="bigmodel" vbProcedure="false">OFFSET([1]基本信息!$A$1,0,0,COUNTA([1]基本信息!$A$1)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="CMRight" vbProcedure="false">"'[3]'!$l$6":"$l$10"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="crlist" vbProcedure="false">OFFSET([1]Review记录!$A$3,0,0,COUNTA([1]Review记录!$K$1:$K$1048576),24)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="endcol" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="endline" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="from" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="KOUMOKUSUU" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="moduleList" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="Module_num" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="question" vbProcedure="false">OFFSET([1]Review记录!$K$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="questionType" vbProcedure="false">OFFSET([1]Review记录!$Q$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="reporter" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-3,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="ReviewKind" vbProcedure="false">[2]信息定义!$H$6:$H$8</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="StatOKNG" vbProcedure="false">[2]信息定义!$J$6:$J$11</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="StatOpenClose" vbProcedure="false">[2]信息定义!$K$6:$K$10</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="status" vbProcedure="false">OFFSET([1]Review记录!$V$3,1,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="StatYesNo" vbProcedure="false">[2]信息定义!$I$6:$I$10</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="TestPhase" vbProcedure="false">"'[1]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="total" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$Z$1:$Z$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="worker" vbProcedure="false">OFFSET([1]Review记录!$A$1,0,0,COUNTA([1]Review记录!$K$1:$K$1048576)-1,1)</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="一级标题" vbProcedure="false">"'[5]'!$b$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品名称与版本" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品效益分析" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品概述" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品目标" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品目标市场" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="产品竞争分析" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="任务分解" vbProcedure="false">"'[3]'!$b$54"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="供方协定管理计划" vbProcedure="false">"'[3]'!$b$165"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="信息内容" vbProcedure="false">"'[3]'!$b$2"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="假定约束条件" vbProcedure="false">"'[3]'!$b$14"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="共利益者管理" vbProcedure="false">"'[3]'!$b$168"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="关键依赖关系" vbProcedure="false">"'[3]'!$b$174"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="关键问题" vbProcedure="false">"'[3]'!$b$25"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="决策分析计划" vbProcedure="false">"'[3]'!$b$182"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="可升级目标" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="可用性目标" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="可维护性目标" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="可靠性目标" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="培训计划" vbProcedure="false">"'[3]'!$b$149"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="子活动类型名" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="客户财产" vbProcedure="false">"'[3]'!$b$130"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="度量计划" vbProcedure="false">"'[3]'!$b$186"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="成本预算" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="模块" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="沟通" vbProcedure="false">"'[3]'!$b$169"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="父活动类型名" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="生命周期模型选定" vbProcedure="false">"'[3]'!$b$46"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="约束条件" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="规模与工作量估计" vbProcedure="false">"'[3]'!$b$56"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="规模和工作量估计" vbProcedure="false">"'[3]'!$b$73"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="识别知识和技能" vbProcedure="false">"'[3]'!$b$138"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="识别项目风险" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="质量保证计划" vbProcedure="false">"'[3]'!$b$206"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="软件复用" vbProcedure="false">"'[3]'!$b$88"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="运行环境" vbProcedure="false">"'[3]'!$b$116"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="配置管理" vbProcedure="false">"'[3]'!$b$209"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="配置管理计划" vbProcedure="false">"'[3]'!$b$201"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="里程碑" vbProcedure="false">NA()</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="需求信息" vbProcedure="false">"'[3]'!$b$29"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="需求开发工具" vbProcedure="false">"'[3]'!$b$35"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目专属资源" vbProcedure="false">"'[3]'!$b$95"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目估计" vbProcedure="false">"'[3]'!$b$72"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目信息" vbProcedure="false">"'[3]'!$b$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目名称" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目培训" vbProcedure="false">"'[3]'!$b$137"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目基本信息" vbProcedure="false">"'[3]'!$b$5"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目概述" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目监控计划" vbProcedure="false">"'[3]'!$b$157"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目目标" vbProcedure="false">"'[3]'!$b$22"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目目的" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目组角色与职责" vbProcedure="false">"'[3]'!$b$97"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目范围" vbProcedure="false">"'[3]'!$b$53"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目规模" vbProcedure="false">"'[3]'!$a$1"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目资源" vbProcedure="false">"'[3]'!$b$96"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目过程定义" vbProcedure="false">"'[3]'!$b$45"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目过程裁剪" vbProcedure="false">"'[3]'!$b$50"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目阶段和里程碑" vbProcedure="false">"'[3]'!$b$58"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="项目需求" vbProcedure="false">"'[3]'!$b$28"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="风险管理" vbProcedure="false">"'[3]'!$b$202"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" name="风险管理计划" vbProcedure="false">"'[3]'!$b$194"</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" localSheetId="0" name="Print_Titles" vbProcedure="false">需求进度管理表!$1:$3</ns0:definedName>
+    <ns0:definedName function="false" hidden="false" localSheetId="1" name="Print_Titles" vbProcedure="false">示例!$1:$3</ns0:definedName>
+  </ns0:definedNames>
+  <ns0:calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <ns0:extLst>
+    <ns0:ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <ns2:extCalcPr stringRefSyntax="CalcA1"/>
+    </ns0:ext>
+  </ns0:extLst>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1183,1239 +1183,1405 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="B1:J168"/>
-  <sheetFormatPr defaultColWidth="9.859375" defaultRowHeight="11.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="4.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="18.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="62.76"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="6.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="24.26"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="1" width="9.85"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" s="7" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" s="12" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" s="12" customFormat="true" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="24"/>
-    </row>
-    <row r="30" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="24"/>
-    </row>
-    <row r="31" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="24"/>
-    </row>
-    <row r="32" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="24"/>
-    </row>
-    <row r="33" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="24"/>
-    </row>
-    <row r="34" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24"/>
-    </row>
-    <row r="35" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="24"/>
-    </row>
-    <row r="36" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="24"/>
-    </row>
-    <row r="37" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="24"/>
-    </row>
-    <row r="38" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="24"/>
-    </row>
-    <row r="39" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="24"/>
-    </row>
-    <row r="40" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="24"/>
-    </row>
-    <row r="41" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="24"/>
-    </row>
-    <row r="42" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="24"/>
-    </row>
-    <row r="43" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="24"/>
-    </row>
-    <row r="44" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="24"/>
-    </row>
-    <row r="45" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="24"/>
-    </row>
-    <row r="46" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="24"/>
-    </row>
-    <row r="47" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="24"/>
-    </row>
-    <row r="48" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="24"/>
-    </row>
-    <row r="49" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="24"/>
-    </row>
-    <row r="50" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="24"/>
-    </row>
-    <row r="51" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="24"/>
-    </row>
-    <row r="52" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="24"/>
-    </row>
-    <row r="53" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="24"/>
-    </row>
-    <row r="54" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="24"/>
-    </row>
-    <row r="55" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="24"/>
-    </row>
-    <row r="56" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="24"/>
-    </row>
-    <row r="57" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="24"/>
-    </row>
-    <row r="58" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="24"/>
-    </row>
-    <row r="59" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="24"/>
-    </row>
-    <row r="60" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="24"/>
-    </row>
-    <row r="61" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="24"/>
-    </row>
-    <row r="62" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="24"/>
-    </row>
-    <row r="63" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="24"/>
-    </row>
-    <row r="64" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="24"/>
-    </row>
-    <row r="65" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="24"/>
-    </row>
-    <row r="66" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="24"/>
-    </row>
-    <row r="67" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="24"/>
-    </row>
-    <row r="68" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="24"/>
-    </row>
-    <row r="69" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="24"/>
-    </row>
-    <row r="70" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="24"/>
-    </row>
-    <row r="71" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="24"/>
-    </row>
-    <row r="72" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="24"/>
-    </row>
-    <row r="73" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="24"/>
-    </row>
-    <row r="74" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="24"/>
-    </row>
-    <row r="75" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="24"/>
-    </row>
-    <row r="76" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="24"/>
-    </row>
-    <row r="77" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="24"/>
-    </row>
-    <row r="78" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="24"/>
-    </row>
-    <row r="79" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="24"/>
-    </row>
-    <row r="80" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="24"/>
-    </row>
-    <row r="81" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="24"/>
-    </row>
-    <row r="82" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="24"/>
-    </row>
-    <row r="83" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="24"/>
-    </row>
-    <row r="84" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="24"/>
-    </row>
-    <row r="85" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="24"/>
-    </row>
-    <row r="86" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="24"/>
-    </row>
-    <row r="87" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="24"/>
-    </row>
-    <row r="88" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="24"/>
-    </row>
-    <row r="89" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="24"/>
-    </row>
-    <row r="90" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="24"/>
-    </row>
-    <row r="91" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="24"/>
-    </row>
-    <row r="92" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="24"/>
-    </row>
-    <row r="93" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="24"/>
-    </row>
-    <row r="94" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="24"/>
-    </row>
-    <row r="95" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="24"/>
-    </row>
-    <row r="96" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="24"/>
-    </row>
-    <row r="97" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="24"/>
-    </row>
-    <row r="98" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="24"/>
-    </row>
-    <row r="99" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="24"/>
-    </row>
-    <row r="100" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="24"/>
-    </row>
-    <row r="101" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="24"/>
-    </row>
-    <row r="102" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="24"/>
-    </row>
-    <row r="103" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="24"/>
-    </row>
-    <row r="104" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="24"/>
-    </row>
-    <row r="105" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="24"/>
-    </row>
-    <row r="106" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="24"/>
-    </row>
-    <row r="107" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="24"/>
-    </row>
-    <row r="108" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="24"/>
-    </row>
-    <row r="109" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="24"/>
-    </row>
-    <row r="110" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="24"/>
-    </row>
-    <row r="111" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="24"/>
-    </row>
-    <row r="112" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="24"/>
-    </row>
-    <row r="113" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="24"/>
-    </row>
-    <row r="114" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="24"/>
-    </row>
-    <row r="115" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="24"/>
-    </row>
-    <row r="116" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="24"/>
-    </row>
-    <row r="117" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="24"/>
-    </row>
-    <row r="118" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="24"/>
-    </row>
-    <row r="119" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="24"/>
-    </row>
-    <row r="120" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="24"/>
-    </row>
-    <row r="121" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="24"/>
-    </row>
-    <row r="122" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="24"/>
-    </row>
-    <row r="123" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="24"/>
-    </row>
-    <row r="124" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="24"/>
-    </row>
-    <row r="125" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="24"/>
-    </row>
-    <row r="126" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="24"/>
-    </row>
-    <row r="127" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="24"/>
-    </row>
-    <row r="128" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="24"/>
-    </row>
-    <row r="129" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="24"/>
-    </row>
-    <row r="130" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="24"/>
-    </row>
-    <row r="131" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="24"/>
-    </row>
-    <row r="132" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="24"/>
-    </row>
-    <row r="133" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="24"/>
-    </row>
-    <row r="134" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="24"/>
-    </row>
-    <row r="135" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="24"/>
-    </row>
-    <row r="136" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="24"/>
-    </row>
-    <row r="137" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="24"/>
-    </row>
-    <row r="138" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="24"/>
-    </row>
-    <row r="139" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="24"/>
-    </row>
-    <row r="140" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="24"/>
-    </row>
-    <row r="141" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="24"/>
-    </row>
-    <row r="142" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="24"/>
-    </row>
-    <row r="143" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="24"/>
-    </row>
-    <row r="144" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="24"/>
-    </row>
-    <row r="145" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="24"/>
-    </row>
-    <row r="146" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="24"/>
-    </row>
-    <row r="147" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="24"/>
-    </row>
-    <row r="148" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="24"/>
-    </row>
-    <row r="149" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="24"/>
-    </row>
-    <row r="150" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="24"/>
-    </row>
-    <row r="151" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="24"/>
-    </row>
-    <row r="152" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="24"/>
-    </row>
-    <row r="153" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="24"/>
-    </row>
-    <row r="154" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="24"/>
-    </row>
-    <row r="155" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="24"/>
-    </row>
-    <row r="156" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="24"/>
-    </row>
-    <row r="157" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="24"/>
-    </row>
-    <row r="158" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="24"/>
-    </row>
-    <row r="159" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="24"/>
-    </row>
-    <row r="160" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="24"/>
-    </row>
-    <row r="161" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="24"/>
-    </row>
-    <row r="162" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="24"/>
-    </row>
-    <row r="163" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="24"/>
-    </row>
-    <row r="164" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="24"/>
-    </row>
-    <row r="165" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="24"/>
-    </row>
-    <row r="166" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="24"/>
-    </row>
-    <row r="167" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="24"/>
-    </row>
-    <row r="168" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="24"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="0.979861111111111" bottom="0.979861111111111" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr filterMode="false">
+    <ns0:pageSetUpPr fitToPage="true"/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="B1:J168"/>
+  <ns0:sheetFormatPr defaultColWidth="9.859375" defaultRowHeight="11.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <ns0:cols>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.77"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="4.83"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="18.24"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="62.76"/>
+    <ns0:col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.85"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11.41"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="6.91"/>
+    <ns0:col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="24.26"/>
+    <ns0:col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="1" width="9.85"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B1" s="5" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="5"/>
+      <ns0:c r="D1" s="5"/>
+      <ns0:c r="E1" s="5"/>
+      <ns0:c r="F1" s="5"/>
+    </ns0:row>
+    <ns0:row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B2" s="6" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="6"/>
+      <ns0:c r="D2" s="6"/>
+      <ns0:c r="E2" s="6"/>
+      <ns0:c r="F2" s="6"/>
+    </ns0:row>
+    <ns0:row r="3" s="7" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B3" s="8" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="9" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="9" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="9" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="10" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="10" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="11" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="11" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="J3" s="11" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>重构验收依据/限制</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" s="12" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B4" s="13" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="14" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" s="14" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="14" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="F4" s="14" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="G4" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H4" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-03</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I4" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J4" s="18" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B5" s="19" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="20" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="20" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="20" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="F5" s="20" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="G5" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-04</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I5" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J5" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6" s="12" customFormat="true" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B6" s="13" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="20" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="20" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="20" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="20" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-04</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" s="18" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B7" s="19" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="20" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="20" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="20" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="20" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="15" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I7" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>△</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J7" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>在线定位依赖Key；服务器站点及推荐测试通过</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B8" s="13" t="n">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="20" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="20" t="s">
+        <ns0:v>29</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="20" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="20" t="s">
+        <ns0:v>31</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" s="15" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>△</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J8" s="18" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+      <ns0:c r="K8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WebEngine及双模式实现；腾讯在线Key未配置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B9" s="19" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="20" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="20" t="s">
+        <ns0:v>33</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="20" t="s">
+        <ns0:v>34</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="20" t="s">
+        <ns0:v>35</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="15" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I9" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J9" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B10" s="13" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="20" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="20" t="s">
+        <ns0:v>36</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="20" t="s">
+        <ns0:v>37</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="20" t="s">
+        <ns0:v>38</ns0:v>
+      </ns0:c>
+      <ns0:c r="G10" s="15" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="H10" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I10" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J10" s="18" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="K10" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B11" s="19" t="n">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" s="20" t="s">
+        <ns0:v>41</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" s="20" t="s">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11" s="20" t="s">
+        <ns0:v>43</ns0:v>
+      </ns0:c>
+      <ns0:c r="G11" s="15" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I11" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J11" s="18" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="K11" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B12" s="13" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D12" s="20" t="s">
+        <ns0:v>45</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" s="20" t="s">
+        <ns0:v>46</ns0:v>
+      </ns0:c>
+      <ns0:c r="F12" s="20" t="s">
+        <ns0:v>47</ns0:v>
+      </ns0:c>
+      <ns0:c r="G12" s="15" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="H12" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I12" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J12" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B13" s="19" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D13" s="20" t="s">
+        <ns0:v>48</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" s="20" t="s">
+        <ns0:v>49</ns0:v>
+      </ns0:c>
+      <ns0:c r="F13" s="20" t="s">
+        <ns0:v>50</ns0:v>
+      </ns0:c>
+      <ns0:c r="G13" s="15" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="H13" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I13" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J13" s="18" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="K13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B14" s="13" t="n">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" s="20" t="s">
+        <ns0:v>51</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" s="20" t="s">
+        <ns0:v>52</ns0:v>
+      </ns0:c>
+      <ns0:c r="F14" s="20" t="s">
+        <ns0:v>53</ns0:v>
+      </ns0:c>
+      <ns0:c r="G14" s="15" t="s">
+        <ns0:v>44</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I14" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J14" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B15" s="19" t="n">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="C15" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D15" s="20" t="s">
+        <ns0:v>54</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" s="20" t="s">
+        <ns0:v>55</ns0:v>
+      </ns0:c>
+      <ns0:c r="F15" s="20" t="s">
+        <ns0:v>56</ns0:v>
+      </ns0:c>
+      <ns0:c r="G15" s="15" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="H15" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I15" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J15" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B16" s="13" t="n">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="C16" s="20" t="s">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" s="20" t="s">
+        <ns0:v>58</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" s="20" t="s">
+        <ns0:v>59</ns0:v>
+      </ns0:c>
+      <ns0:c r="F16" s="20" t="s">
+        <ns0:v>60</ns0:v>
+      </ns0:c>
+      <ns0:c r="G16" s="15" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="H16" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I16" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J16" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B17" s="19" t="n">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="C17" s="20" t="s">
+        <ns0:v>61</ns0:v>
+      </ns0:c>
+      <ns0:c r="D17" s="20" t="s">
+        <ns0:v>62</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" s="20" t="s">
+        <ns0:v>63</ns0:v>
+      </ns0:c>
+      <ns0:c r="F17" s="20" t="s">
+        <ns0:v>64</ns0:v>
+      </ns0:c>
+      <ns0:c r="G17" s="15" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="H17" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-05</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I17" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J17" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B18" s="13" t="n">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="C18" s="20" t="s">
+        <ns0:v>61</ns0:v>
+      </ns0:c>
+      <ns0:c r="D18" s="20" t="s">
+        <ns0:v>65</ns0:v>
+      </ns0:c>
+      <ns0:c r="E18" s="20" t="s">
+        <ns0:v>66</ns0:v>
+      </ns0:c>
+      <ns0:c r="F18" s="20" t="s">
+        <ns0:v>67</ns0:v>
+      </ns0:c>
+      <ns0:c r="G18" s="15" t="s">
+        <ns0:v>57</ns0:v>
+      </ns0:c>
+      <ns0:c r="H18" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-06</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I18" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J18" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B19" s="19" t="n">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="C19" s="20" t="s">
+        <ns0:v>68</ns0:v>
+      </ns0:c>
+      <ns0:c r="D19" s="20" t="s">
+        <ns0:v>69</ns0:v>
+      </ns0:c>
+      <ns0:c r="E19" s="20" t="s">
+        <ns0:v>70</ns0:v>
+      </ns0:c>
+      <ns0:c r="F19" s="20" t="s">
+        <ns0:v>71</ns0:v>
+      </ns0:c>
+      <ns0:c r="G19" s="15" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="H19" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-06</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I19" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>△</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J19" s="18" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="K19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>HTTP对账通过；浏览器断网恢复验收继续</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B20" s="13" t="n">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="C20" s="20" t="s">
+        <ns0:v>73</ns0:v>
+      </ns0:c>
+      <ns0:c r="D20" s="20" t="s">
+        <ns0:v>74</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" s="20" t="s">
+        <ns0:v>75</ns0:v>
+      </ns0:c>
+      <ns0:c r="F20" s="20" t="s">
+        <ns0:v>76</ns0:v>
+      </ns0:c>
+      <ns0:c r="G20" s="15" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="H20" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I20" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>△</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J20" s="18" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="K20" t="inlineStr">
+        <ns0:is>
+          <ns0:t>站级简化模型1/6/24h已验；未实现天气节假日多维及桩级ML</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="21" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B21" s="19" t="n">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="C21" s="20" t="s">
+        <ns0:v>77</ns0:v>
+      </ns0:c>
+      <ns0:c r="D21" s="20" t="s">
+        <ns0:v>78</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" s="20" t="s">
+        <ns0:v>79</ns0:v>
+      </ns0:c>
+      <ns0:c r="F21" s="20" t="s">
+        <ns0:v>80</ns0:v>
+      </ns0:c>
+      <ns0:c r="G21" s="15" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="H21" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-08</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I21" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J21" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B22" s="13" t="n">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="C22" s="20" t="s">
+        <ns0:v>77</ns0:v>
+      </ns0:c>
+      <ns0:c r="D22" s="20" t="s">
+        <ns0:v>81</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" s="20" t="s">
+        <ns0:v>82</ns0:v>
+      </ns0:c>
+      <ns0:c r="F22" s="20" t="s">
+        <ns0:v>83</ns0:v>
+      </ns0:c>
+      <ns0:c r="G22" s="15" t="s">
+        <ns0:v>72</ns0:v>
+      </ns0:c>
+      <ns0:c r="H22" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-07</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I22" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J22" s="18" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+      <ns0:c r="K22" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B23" s="19" t="n">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="C23" s="20" t="s">
+        <ns0:v>77</ns0:v>
+      </ns0:c>
+      <ns0:c r="D23" s="20" t="s">
+        <ns0:v>84</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" s="20" t="s">
+        <ns0:v>85</ns0:v>
+      </ns0:c>
+      <ns0:c r="F23" s="20" t="s">
+        <ns0:v>86</ns0:v>
+      </ns0:c>
+      <ns0:c r="G23" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H23" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-09</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I23" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J23" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K23" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B24" s="13" t="n">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="C24" s="20" t="s">
+        <ns0:v>87</ns0:v>
+      </ns0:c>
+      <ns0:c r="D24" s="20" t="s">
+        <ns0:v>88</ns0:v>
+      </ns0:c>
+      <ns0:c r="E24" s="20" t="s">
+        <ns0:v>89</ns0:v>
+      </ns0:c>
+      <ns0:c r="F24" s="20" t="s">
+        <ns0:v>90</ns0:v>
+      </ns0:c>
+      <ns0:c r="G24" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H24" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I24" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>△</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J24" s="18" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="K24" t="inlineStr">
+        <ns0:is>
+          <ns0:t>全量脚本和方案已就绪；最终交付包待生成</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B25" s="13" t="n">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="C25" s="20" t="s">
+        <ns0:v>91</ns0:v>
+      </ns0:c>
+      <ns0:c r="D25" s="20" t="s">
+        <ns0:v>92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E25" s="20" t="s">
+        <ns0:v>93</ns0:v>
+      </ns0:c>
+      <ns0:c r="F25" s="20" t="s">
+        <ns0:v>94</ns0:v>
+      </ns0:c>
+      <ns0:c r="G25" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H25" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I25" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J25" s="18" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="K25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B26" s="13" t="n">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="C26" s="20" t="s">
+        <ns0:v>91</ns0:v>
+      </ns0:c>
+      <ns0:c r="D26" s="20" t="s">
+        <ns0:v>95</ns0:v>
+      </ns0:c>
+      <ns0:c r="E26" s="20" t="s">
+        <ns0:v>96</ns0:v>
+      </ns0:c>
+      <ns0:c r="F26" s="20" t="s">
+        <ns0:v>97</ns0:v>
+      </ns0:c>
+      <ns0:c r="G26" s="15" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H26" s="16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-09-10</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I26" s="17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>○</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J26" s="18" t="s">
+        <ns0:v>39</ns0:v>
+      </ns0:c>
+      <ns0:c r="K26" t="inlineStr">
+        <ns0:is>
+          <ns0:t>实现与测试证据见 docs/需求验收追踪.md；阶段PR30–34</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27" s="12" customFormat="true" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B27" s="19"/>
+      <ns0:c r="C27" s="20"/>
+      <ns0:c r="D27" s="20"/>
+      <ns0:c r="E27" s="20"/>
+      <ns0:c r="F27" s="20"/>
+      <ns0:c r="G27" s="15"/>
+      <ns0:c r="H27" s="16"/>
+      <ns0:c r="I27" s="17"/>
+      <ns0:c r="J27" s="18"/>
+    </ns0:row>
+    <ns0:row r="28" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <ns0:c r="B28" s="21"/>
+      <ns0:c r="C28" s="22"/>
+      <ns0:c r="D28" s="23"/>
+      <ns0:c r="E28" s="22"/>
+      <ns0:c r="F28" s="22"/>
+      <ns0:c r="G28" s="15"/>
+      <ns0:c r="H28" s="16"/>
+      <ns0:c r="I28" s="17"/>
+      <ns0:c r="J28" s="18"/>
+    </ns0:row>
+    <ns0:row r="29" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B29" s="24"/>
+    </ns0:row>
+    <ns0:row r="30" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B30" s="24"/>
+    </ns0:row>
+    <ns0:row r="31" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B31" s="24"/>
+    </ns0:row>
+    <ns0:row r="32" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B32" s="24"/>
+    </ns0:row>
+    <ns0:row r="33" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B33" s="24"/>
+    </ns0:row>
+    <ns0:row r="34" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B34" s="24"/>
+    </ns0:row>
+    <ns0:row r="35" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B35" s="24"/>
+    </ns0:row>
+    <ns0:row r="36" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B36" s="24"/>
+    </ns0:row>
+    <ns0:row r="37" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B37" s="24"/>
+    </ns0:row>
+    <ns0:row r="38" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B38" s="24"/>
+    </ns0:row>
+    <ns0:row r="39" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B39" s="24"/>
+    </ns0:row>
+    <ns0:row r="40" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B40" s="24"/>
+    </ns0:row>
+    <ns0:row r="41" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B41" s="24"/>
+    </ns0:row>
+    <ns0:row r="42" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B42" s="24"/>
+    </ns0:row>
+    <ns0:row r="43" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B43" s="24"/>
+    </ns0:row>
+    <ns0:row r="44" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B44" s="24"/>
+    </ns0:row>
+    <ns0:row r="45" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B45" s="24"/>
+    </ns0:row>
+    <ns0:row r="46" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B46" s="24"/>
+    </ns0:row>
+    <ns0:row r="47" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B47" s="24"/>
+    </ns0:row>
+    <ns0:row r="48" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B48" s="24"/>
+    </ns0:row>
+    <ns0:row r="49" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B49" s="24"/>
+    </ns0:row>
+    <ns0:row r="50" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B50" s="24"/>
+    </ns0:row>
+    <ns0:row r="51" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B51" s="24"/>
+    </ns0:row>
+    <ns0:row r="52" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B52" s="24"/>
+    </ns0:row>
+    <ns0:row r="53" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B53" s="24"/>
+    </ns0:row>
+    <ns0:row r="54" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B54" s="24"/>
+    </ns0:row>
+    <ns0:row r="55" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B55" s="24"/>
+    </ns0:row>
+    <ns0:row r="56" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B56" s="24"/>
+    </ns0:row>
+    <ns0:row r="57" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B57" s="24"/>
+    </ns0:row>
+    <ns0:row r="58" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B58" s="24"/>
+    </ns0:row>
+    <ns0:row r="59" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B59" s="24"/>
+    </ns0:row>
+    <ns0:row r="60" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B60" s="24"/>
+    </ns0:row>
+    <ns0:row r="61" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B61" s="24"/>
+    </ns0:row>
+    <ns0:row r="62" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B62" s="24"/>
+    </ns0:row>
+    <ns0:row r="63" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B63" s="24"/>
+    </ns0:row>
+    <ns0:row r="64" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B64" s="24"/>
+    </ns0:row>
+    <ns0:row r="65" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B65" s="24"/>
+    </ns0:row>
+    <ns0:row r="66" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B66" s="24"/>
+    </ns0:row>
+    <ns0:row r="67" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B67" s="24"/>
+    </ns0:row>
+    <ns0:row r="68" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B68" s="24"/>
+    </ns0:row>
+    <ns0:row r="69" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B69" s="24"/>
+    </ns0:row>
+    <ns0:row r="70" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B70" s="24"/>
+    </ns0:row>
+    <ns0:row r="71" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B71" s="24"/>
+    </ns0:row>
+    <ns0:row r="72" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B72" s="24"/>
+    </ns0:row>
+    <ns0:row r="73" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B73" s="24"/>
+    </ns0:row>
+    <ns0:row r="74" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B74" s="24"/>
+    </ns0:row>
+    <ns0:row r="75" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B75" s="24"/>
+    </ns0:row>
+    <ns0:row r="76" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B76" s="24"/>
+    </ns0:row>
+    <ns0:row r="77" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B77" s="24"/>
+    </ns0:row>
+    <ns0:row r="78" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B78" s="24"/>
+    </ns0:row>
+    <ns0:row r="79" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B79" s="24"/>
+    </ns0:row>
+    <ns0:row r="80" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B80" s="24"/>
+    </ns0:row>
+    <ns0:row r="81" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B81" s="24"/>
+    </ns0:row>
+    <ns0:row r="82" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B82" s="24"/>
+    </ns0:row>
+    <ns0:row r="83" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B83" s="24"/>
+    </ns0:row>
+    <ns0:row r="84" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B84" s="24"/>
+    </ns0:row>
+    <ns0:row r="85" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B85" s="24"/>
+    </ns0:row>
+    <ns0:row r="86" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B86" s="24"/>
+    </ns0:row>
+    <ns0:row r="87" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B87" s="24"/>
+    </ns0:row>
+    <ns0:row r="88" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B88" s="24"/>
+    </ns0:row>
+    <ns0:row r="89" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B89" s="24"/>
+    </ns0:row>
+    <ns0:row r="90" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B90" s="24"/>
+    </ns0:row>
+    <ns0:row r="91" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B91" s="24"/>
+    </ns0:row>
+    <ns0:row r="92" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B92" s="24"/>
+    </ns0:row>
+    <ns0:row r="93" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B93" s="24"/>
+    </ns0:row>
+    <ns0:row r="94" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B94" s="24"/>
+    </ns0:row>
+    <ns0:row r="95" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B95" s="24"/>
+    </ns0:row>
+    <ns0:row r="96" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B96" s="24"/>
+    </ns0:row>
+    <ns0:row r="97" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B97" s="24"/>
+    </ns0:row>
+    <ns0:row r="98" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B98" s="24"/>
+    </ns0:row>
+    <ns0:row r="99" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B99" s="24"/>
+    </ns0:row>
+    <ns0:row r="100" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B100" s="24"/>
+    </ns0:row>
+    <ns0:row r="101" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B101" s="24"/>
+    </ns0:row>
+    <ns0:row r="102" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B102" s="24"/>
+    </ns0:row>
+    <ns0:row r="103" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B103" s="24"/>
+    </ns0:row>
+    <ns0:row r="104" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B104" s="24"/>
+    </ns0:row>
+    <ns0:row r="105" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B105" s="24"/>
+    </ns0:row>
+    <ns0:row r="106" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B106" s="24"/>
+    </ns0:row>
+    <ns0:row r="107" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B107" s="24"/>
+    </ns0:row>
+    <ns0:row r="108" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B108" s="24"/>
+    </ns0:row>
+    <ns0:row r="109" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B109" s="24"/>
+    </ns0:row>
+    <ns0:row r="110" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B110" s="24"/>
+    </ns0:row>
+    <ns0:row r="111" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B111" s="24"/>
+    </ns0:row>
+    <ns0:row r="112" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B112" s="24"/>
+    </ns0:row>
+    <ns0:row r="113" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B113" s="24"/>
+    </ns0:row>
+    <ns0:row r="114" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B114" s="24"/>
+    </ns0:row>
+    <ns0:row r="115" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B115" s="24"/>
+    </ns0:row>
+    <ns0:row r="116" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B116" s="24"/>
+    </ns0:row>
+    <ns0:row r="117" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B117" s="24"/>
+    </ns0:row>
+    <ns0:row r="118" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B118" s="24"/>
+    </ns0:row>
+    <ns0:row r="119" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B119" s="24"/>
+    </ns0:row>
+    <ns0:row r="120" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B120" s="24"/>
+    </ns0:row>
+    <ns0:row r="121" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B121" s="24"/>
+    </ns0:row>
+    <ns0:row r="122" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B122" s="24"/>
+    </ns0:row>
+    <ns0:row r="123" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B123" s="24"/>
+    </ns0:row>
+    <ns0:row r="124" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B124" s="24"/>
+    </ns0:row>
+    <ns0:row r="125" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B125" s="24"/>
+    </ns0:row>
+    <ns0:row r="126" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B126" s="24"/>
+    </ns0:row>
+    <ns0:row r="127" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B127" s="24"/>
+    </ns0:row>
+    <ns0:row r="128" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B128" s="24"/>
+    </ns0:row>
+    <ns0:row r="129" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B129" s="24"/>
+    </ns0:row>
+    <ns0:row r="130" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B130" s="24"/>
+    </ns0:row>
+    <ns0:row r="131" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B131" s="24"/>
+    </ns0:row>
+    <ns0:row r="132" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B132" s="24"/>
+    </ns0:row>
+    <ns0:row r="133" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B133" s="24"/>
+    </ns0:row>
+    <ns0:row r="134" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B134" s="24"/>
+    </ns0:row>
+    <ns0:row r="135" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B135" s="24"/>
+    </ns0:row>
+    <ns0:row r="136" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B136" s="24"/>
+    </ns0:row>
+    <ns0:row r="137" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B137" s="24"/>
+    </ns0:row>
+    <ns0:row r="138" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B138" s="24"/>
+    </ns0:row>
+    <ns0:row r="139" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B139" s="24"/>
+    </ns0:row>
+    <ns0:row r="140" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B140" s="24"/>
+    </ns0:row>
+    <ns0:row r="141" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B141" s="24"/>
+    </ns0:row>
+    <ns0:row r="142" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B142" s="24"/>
+    </ns0:row>
+    <ns0:row r="143" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B143" s="24"/>
+    </ns0:row>
+    <ns0:row r="144" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B144" s="24"/>
+    </ns0:row>
+    <ns0:row r="145" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B145" s="24"/>
+    </ns0:row>
+    <ns0:row r="146" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B146" s="24"/>
+    </ns0:row>
+    <ns0:row r="147" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B147" s="24"/>
+    </ns0:row>
+    <ns0:row r="148" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B148" s="24"/>
+    </ns0:row>
+    <ns0:row r="149" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B149" s="24"/>
+    </ns0:row>
+    <ns0:row r="150" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B150" s="24"/>
+    </ns0:row>
+    <ns0:row r="151" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B151" s="24"/>
+    </ns0:row>
+    <ns0:row r="152" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B152" s="24"/>
+    </ns0:row>
+    <ns0:row r="153" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B153" s="24"/>
+    </ns0:row>
+    <ns0:row r="154" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B154" s="24"/>
+    </ns0:row>
+    <ns0:row r="155" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B155" s="24"/>
+    </ns0:row>
+    <ns0:row r="156" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B156" s="24"/>
+    </ns0:row>
+    <ns0:row r="157" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B157" s="24"/>
+    </ns0:row>
+    <ns0:row r="158" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B158" s="24"/>
+    </ns0:row>
+    <ns0:row r="159" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B159" s="24"/>
+    </ns0:row>
+    <ns0:row r="160" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B160" s="24"/>
+    </ns0:row>
+    <ns0:row r="161" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B161" s="24"/>
+    </ns0:row>
+    <ns0:row r="162" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B162" s="24"/>
+    </ns0:row>
+    <ns0:row r="163" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B163" s="24"/>
+    </ns0:row>
+    <ns0:row r="164" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B164" s="24"/>
+    </ns0:row>
+    <ns0:row r="165" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B165" s="24"/>
+    </ns0:row>
+    <ns0:row r="166" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B166" s="24"/>
+    </ns0:row>
+    <ns0:row r="167" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B167" s="24"/>
+    </ns0:row>
+    <ns0:row r="168" customFormat="false" ht="11.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <ns0:c r="B168" s="24"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:mergeCells count="2">
+    <ns0:mergeCell ref="B1:F1"/>
+    <ns0:mergeCell ref="B2:F2"/>
+  </ns0:mergeCells>
+  <ns0:printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
+  <ns0:pageMargins left="0.75" right="0.75" top="0.979861111111111" bottom="0.979861111111111" header="0.511811023622047" footer="0.511811023622047"/>
+  <ns0:pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <ns0:headerFooter differentFirst="false" differentOddEven="false">
+    <ns0:oddHeader/>
+    <ns0:oddFooter/>
+  </ns0:headerFooter>
+</ns0:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/docs/01需求矩阵第4组张芮萌.xlsx
+++ b/docs/01需求矩阵第4组张芮萌.xlsx
@@ -1849,7 +1849,7 @@
       </ns0:c>
       <ns0:c r="I19" s="17" t="inlineStr">
         <ns0:is>
-          <ns0:t>△</ns0:t>
+          <ns0:t>○</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J19" s="18" t="s">
@@ -1857,7 +1857,7 @@
       </ns0:c>
       <ns0:c r="K19" t="inlineStr">
         <ns0:is>
-          <ns0:t>HTTP对账通过；浏览器断网恢复验收继续</ns0:t>
+          <ns0:t>HTTP营收对账+WebEngine实时/断线恢复/零值/两尺寸截图通过</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2039,7 +2039,7 @@
       </ns0:c>
       <ns0:c r="I24" s="17" t="inlineStr">
         <ns0:is>
-          <ns0:t>△</ns0:t>
+          <ns0:t>○</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="J24" s="18" t="s">
@@ -2047,7 +2047,7 @@
       </ns0:c>
       <ns0:c r="K24" t="inlineStr">
         <ns0:is>
-          <ns0:t>全量脚本和方案已就绪；最终交付包待生成</ns0:t>
+          <ns0:t>9fbd20ba：27任务通过；源码/证据包校验及解压构建通过，见测试执行结果</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>

--- a/docs/01需求矩阵第4组张芮萌.xlsx
+++ b/docs/01需求矩阵第4组张芮萌.xlsx
@@ -1439,7 +1439,7 @@
       </ns0:c>
       <ns0:c r="K8" t="inlineStr">
         <ns0:is>
-          <ns0:t>WebEngine及双模式实现；腾讯在线Key未配置</ns0:t>
+          <ns0:t>2026-09-16组长明确暂缓导航；Key已提供，配额121及网页步行显示公交问题保留草稿PR37</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
